--- a/condiciones_listaA.xlsx
+++ b/condiciones_listaA.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98EF3EE8-8252-49FF-A3A4-2A1014188EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{6703B6BF-F000-499E-ADA1-67C2A75608D8}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{6703B6BF-F000-499E-ADA1-67C2A75608D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
